--- a/V6_NAMES_AND_LADDERS.xlsx
+++ b/V6_NAMES_AND_LADDERS.xlsx
@@ -2243,7 +2243,7 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>generic (base added again)</t>
+          <t>set step (IMPROVE_STEP, r666)</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>BUG TODAY: each improvement RAISES its Focus cost (10, 20, 30...), because the generic rule adds the base to every number.</t>
+          <t>Fixed in r666: 1 Focus cheaper a step (10 9 8 7 6 3).</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>generic (base added again)</t>
+          <t>set step (IMPROVE_STEP, r666)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       <c r="R48" s="3" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>BUG TODAY: each improvement RAISES its Focus cost (10, 20, 30...), because the generic rule adds the base to every number. Shared names: All In also offered for Pip In.</t>
+          <t>Fixed in r666: cost stays 10, hands still +3 a step (3 6 9 12 15 24). Shared names: All In also offered for Pip In.</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       <c r="I80" s="3" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>generic (base added again)</t>
+          <t>set step (IMPROVE_STEP, r666)</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -7171,7 +7171,7 @@
       <c r="R80" s="3" t="inlineStr"/>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>BUG TODAY: each improvement RAISES its Focus cost (10, 20, 30...), because the generic rule adds the base to every number.</t>
+          <t>Fixed in r666: cost stays 10, seconds still +10 a step (10 20 30 40 50 80).</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18231,7 @@
       <c r="I213" s="3" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>generic (base added again)</t>
+          <t>set step (IMPROVE_STEP, r666)</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -18272,7 +18272,7 @@
       <c r="R213" s="3" t="inlineStr"/>
       <c r="S213" s="2" t="inlineStr">
         <is>
-          <t>BUG TODAY: each improvement RAISES its Focus cost (10, 20, 30...), because the generic rule adds the base to every number.</t>
+          <t>Fixed in r666: 1 Focus cheaper a step (10 9 8 7 6 3).</t>
         </is>
       </c>
     </row>
